--- a/10aug2026/Surveyv + Gpx.xlsx
+++ b/10aug2026/Surveyv + Gpx.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Barqaab\10aug2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71575036-F600-4B77-A741-EB0E4FB42B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77642C0-4D62-410A-ACC9-C0806D88CD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HtSurveyForm - 081025" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="8" r:id="rId2"/>
-    <sheet name="Gpx - 081025" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId4"/>
-    <sheet name="mdb_gps_points" sheetId="7" r:id="rId5"/>
-    <sheet name="Requirement Specs" sheetId="3" r:id="rId6"/>
+    <sheet name="Mapping" sheetId="10" r:id="rId3"/>
+    <sheet name="Gpx - 081025" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId5"/>
+    <sheet name="mdb_gps_points" sheetId="7" r:id="rId6"/>
+    <sheet name="Requirement Specs" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">mdb_gps_points!$A$1:$AB$1086</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">mdb_gps_points!$A$1:$AB$1086</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -112,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3350" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3427" uniqueCount="246">
   <si>
     <t>Data Form for HT (GIS Survey Barqaab - PPL - OMS Consortium)</t>
   </si>
@@ -732,6 +733,180 @@
   <si>
     <t>Inspectors: Sajjad Ahmed</t>
   </si>
+  <si>
+    <t>pole_typ</t>
+  </si>
+  <si>
+    <t>Already have heder information told by serveyer</t>
+  </si>
+  <si>
+    <t>from top left 2 right</t>
+  </si>
+  <si>
+    <t>Equipment Number</t>
+  </si>
+  <si>
+    <t>Mapping</t>
+  </si>
+  <si>
+    <t>Equipment Size</t>
+  </si>
+  <si>
+    <t>Equipment Phase</t>
+  </si>
+  <si>
+    <t>Equipment Use</t>
+  </si>
+  <si>
+    <t>Equipment Status</t>
+  </si>
+  <si>
+    <t>Mounting</t>
+  </si>
+  <si>
+    <t>Dedicated Consumer Name</t>
+  </si>
+  <si>
+    <t>Equipment Make</t>
+  </si>
+  <si>
+    <t>Equipment Location</t>
+  </si>
+  <si>
+    <t>Form Field</t>
+  </si>
+  <si>
+    <t>Table Field_Data field</t>
+  </si>
+  <si>
+    <t>Number of feeders</t>
+  </si>
+  <si>
+    <t>Pole Class</t>
+  </si>
+  <si>
+    <t>Pole Height</t>
+  </si>
+  <si>
+    <t>End Type</t>
+  </si>
+  <si>
+    <t>All Phase</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Pole Phase</t>
+  </si>
+  <si>
+    <t>Single Phase</t>
+  </si>
+  <si>
+    <t>Three Phase</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>Street Light</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Pole_Type</t>
+  </si>
+  <si>
+    <t>pole_height</t>
+  </si>
+  <si>
+    <t>end_type (sde, dde)</t>
+  </si>
+  <si>
+    <t>pole_phase (R-Y-B-N)</t>
+  </si>
+  <si>
+    <t>equip_status</t>
+  </si>
+  <si>
+    <t>equip_size</t>
+  </si>
+  <si>
+    <t>equip_use</t>
+  </si>
+  <si>
+    <t>equip_number</t>
+  </si>
+  <si>
+    <t>equip_phase</t>
+  </si>
+  <si>
+    <t>transformer_make</t>
+  </si>
+  <si>
+    <t>transformer_location</t>
+  </si>
+  <si>
+    <t>transformer_mounting</t>
+  </si>
+  <si>
+    <t>consumer_name</t>
+  </si>
+  <si>
+    <t>Equipment Type</t>
+  </si>
+  <si>
+    <t>equip_type</t>
+  </si>
+  <si>
+    <t>feeders_on_pole</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>rs_con1</t>
+  </si>
+  <si>
+    <t>rs_con3</t>
+  </si>
+  <si>
+    <t>sc_con</t>
+  </si>
+  <si>
+    <t>lc_con</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>commercial</t>
+  </si>
+  <si>
+    <t>Industrial</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>si_con</t>
+  </si>
+  <si>
+    <t>li_con</t>
+  </si>
+  <si>
+    <t>pb_con</t>
+  </si>
+  <si>
+    <t>st_con</t>
+  </si>
+  <si>
+    <t>ag_con</t>
+  </si>
 </sst>
 </file>
 
@@ -1086,7 +1261,7 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1171,59 +1346,48 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="10" xfId="3"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1234,7 +1398,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1279,6 +1455,15 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1294,32 +1479,23 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1330,6 +1506,19 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Accent2" xfId="4" builtinId="33"/>
@@ -1747,13 +1936,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:colOff>57150</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>47625</xdr:colOff>
       <xdr:row>40</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
@@ -1778,7 +1967,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8572500" y="5645150"/>
+          <a:off x="8591550" y="5645150"/>
           <a:ext cx="1819275" cy="1847850"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2000,6 +2189,187 @@
         <a:xfrm>
           <a:off x="977900" y="14287500"/>
           <a:ext cx="7886700" cy="2162175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>184649</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>63560</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15C338FA-CAE5-6E26-931C-B3C5DBA758F2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="184150"/>
+          <a:ext cx="9715999" cy="1168460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>781319</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>50869</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FCF0DDB-05CD-E323-59F5-5215772FE391}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2025650"/>
+          <a:ext cx="5239019" cy="1339919"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>571729</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>108022</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BA3FB68-08F1-6B09-DEFB-C41C4BD55290}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="571500" y="5156200"/>
+          <a:ext cx="4457929" cy="1397072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>844836</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>88977</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3900BD3D-548D-7DCD-2F14-6E2F98004822}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="342900" y="8343900"/>
+          <a:ext cx="5569236" cy="1505027"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2333,318 +2703,318 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="21">
-      <c r="A1" s="62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
-      <c r="AD1" s="63"/>
-      <c r="AE1" s="63"/>
-      <c r="AF1" s="63"/>
-      <c r="AG1" s="64"/>
+      <c r="A1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
+      <c r="P1" s="60"/>
+      <c r="Q1" s="60"/>
+      <c r="R1" s="60"/>
+      <c r="S1" s="60"/>
+      <c r="T1" s="60"/>
+      <c r="U1" s="60"/>
+      <c r="V1" s="60"/>
+      <c r="W1" s="60"/>
+      <c r="X1" s="60"/>
+      <c r="Y1" s="60"/>
+      <c r="Z1" s="60"/>
+      <c r="AA1" s="60"/>
+      <c r="AB1" s="60"/>
+      <c r="AC1" s="60"/>
+      <c r="AD1" s="60"/>
+      <c r="AE1" s="60"/>
+      <c r="AF1" s="60"/>
+      <c r="AG1" s="61"/>
     </row>
     <row r="2" spans="1:33">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
-      <c r="H2" s="87"/>
-      <c r="I2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="80" t="s">
+      <c r="B2" s="63"/>
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="93"/>
+      <c r="K2" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="71" t="s">
+      <c r="L2" s="85"/>
+      <c r="M2" s="85"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="77" t="s">
+      <c r="P2" s="73"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="78"/>
-      <c r="T2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="80"/>
       <c r="U2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="V2" s="86">
+      <c r="V2" s="90">
         <v>4812</v>
       </c>
-      <c r="W2" s="87"/>
-      <c r="X2" s="50" t="s">
+      <c r="W2" s="91"/>
+      <c r="X2" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="Y2" s="51"/>
-      <c r="Z2" s="51"/>
-      <c r="AA2" s="51"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="51"/>
-      <c r="AD2" s="51"/>
-      <c r="AE2" s="52"/>
-      <c r="AF2" s="69" t="s">
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="63"/>
+      <c r="AA2" s="63"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="63"/>
+      <c r="AD2" s="63"/>
+      <c r="AE2" s="93"/>
+      <c r="AF2" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="AG2" s="70"/>
+      <c r="AG2" s="71"/>
     </row>
     <row r="3" spans="1:33">
-      <c r="A3" s="59" t="s">
+      <c r="A3" s="64" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="65"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="60"/>
-      <c r="K3" s="83" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="66"/>
+      <c r="K3" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="85"/>
-      <c r="O3" s="74" t="s">
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="89"/>
+      <c r="O3" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="76"/>
-      <c r="R3" s="44" t="s">
+      <c r="P3" s="76"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="45"/>
-      <c r="T3" s="46"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="83"/>
       <c r="U3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="V3" s="47">
+      <c r="V3" s="94">
         <v>48123</v>
       </c>
-      <c r="W3" s="48"/>
-      <c r="X3" s="44"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="45"/>
-      <c r="AA3" s="45"/>
-      <c r="AB3" s="45"/>
-      <c r="AC3" s="45"/>
-      <c r="AD3" s="45"/>
-      <c r="AE3" s="45"/>
-      <c r="AF3" s="45"/>
-      <c r="AG3" s="46"/>
+      <c r="W3" s="95"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="82"/>
+      <c r="AC3" s="82"/>
+      <c r="AD3" s="82"/>
+      <c r="AE3" s="82"/>
+      <c r="AF3" s="82"/>
+      <c r="AG3" s="83"/>
     </row>
     <row r="4" spans="1:33">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="67" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="66" t="s">
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="67" t="s">
         <v>171</v>
       </c>
-      <c r="O4" s="68"/>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-      <c r="AB4" s="54"/>
-      <c r="AC4" s="54"/>
-      <c r="AD4" s="54"/>
-      <c r="AE4" s="54"/>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="55"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+      <c r="AA4" s="97"/>
+      <c r="AB4" s="97"/>
+      <c r="AC4" s="97"/>
+      <c r="AD4" s="97"/>
+      <c r="AE4" s="97"/>
+      <c r="AF4" s="97"/>
+      <c r="AG4" s="98"/>
     </row>
     <row r="5" spans="1:33">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="89" t="s">
+      <c r="C5" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="90"/>
-      <c r="L5" s="90"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="96" t="s">
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="96"/>
+      <c r="O5" s="47"/>
       <c r="P5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="Q5" s="58" t="s">
+      <c r="Q5" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58" t="s">
+      <c r="R5" s="50"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="58"/>
-      <c r="AA5" s="58"/>
-      <c r="AB5" s="58"/>
-      <c r="AC5" s="58"/>
-      <c r="AD5" s="58"/>
-      <c r="AE5" s="58"/>
-      <c r="AF5" s="58"/>
-      <c r="AG5" s="57" t="s">
+      <c r="U5" s="50"/>
+      <c r="V5" s="50"/>
+      <c r="W5" s="50"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="50"/>
+      <c r="Z5" s="50"/>
+      <c r="AA5" s="50"/>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="50"/>
+      <c r="AE5" s="50"/>
+      <c r="AF5" s="50"/>
+      <c r="AG5" s="58" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:33">
-      <c r="A6" s="93"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="57" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="57"/>
-      <c r="E6" s="95" t="s">
+      <c r="D6" s="58"/>
+      <c r="E6" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="95"/>
-      <c r="G6" s="95"/>
-      <c r="H6" s="95"/>
-      <c r="I6" s="95"/>
-      <c r="J6" s="95"/>
-      <c r="K6" s="56" t="s">
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="61" t="s">
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="97" t="s">
+      <c r="O6" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="P6" s="49" t="s">
+      <c r="P6" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="Q6" s="56" t="s">
+      <c r="Q6" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="56" t="s">
+      <c r="R6" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="T6" s="61" t="s">
+      <c r="T6" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="U6" s="61" t="s">
+      <c r="U6" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="61" t="s">
+      <c r="V6" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="W6" s="49" t="s">
+      <c r="W6" s="46" t="s">
         <v>18</v>
       </c>
       <c r="X6" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="Y6" s="49" t="s">
+      <c r="Y6" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="Z6" s="49" t="s">
+      <c r="Z6" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="AA6" s="61" t="s">
+      <c r="AA6" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="AB6" s="49" t="s">
+      <c r="AB6" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="AC6" s="49" t="s">
+      <c r="AC6" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="AD6" s="49" t="s">
+      <c r="AD6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="AE6" s="61" t="s">
+      <c r="AE6" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="AF6" s="61" t="s">
+      <c r="AF6" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="AG6" s="57"/>
+      <c r="AG6" s="58"/>
     </row>
     <row r="7" spans="1:33" ht="20" customHeight="1">
-      <c r="A7" s="94"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
+      <c r="A7" s="56"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="16" t="s">
         <v>7</v>
       </c>
@@ -2663,31 +3033,31 @@
       <c r="J7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="49"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="49"/>
-      <c r="U7" s="49"/>
-      <c r="V7" s="49"/>
-      <c r="W7" s="49"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
       <c r="X7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="Y7" s="49"/>
-      <c r="Z7" s="49"/>
-      <c r="AA7" s="49"/>
-      <c r="AB7" s="49"/>
-      <c r="AC7" s="49"/>
-      <c r="AD7" s="49"/>
-      <c r="AE7" s="49"/>
-      <c r="AF7" s="49"/>
-      <c r="AG7" s="57"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="46"/>
+      <c r="AA7" s="46"/>
+      <c r="AB7" s="46"/>
+      <c r="AC7" s="46"/>
+      <c r="AD7" s="46"/>
+      <c r="AE7" s="46"/>
+      <c r="AF7" s="46"/>
+      <c r="AG7" s="58"/>
     </row>
     <row r="8" spans="1:33">
       <c r="A8" s="1">
@@ -3526,23 +3896,22 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="AF6:AF7"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="Q6:Q7"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="V6:V7"/>
-    <mergeCell ref="C5:M5"/>
-    <mergeCell ref="AD6:AD7"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="AE6:AE7"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="W6:W7"/>
+    <mergeCell ref="X2:AE2"/>
+    <mergeCell ref="P4:AG4"/>
+    <mergeCell ref="K6:M7"/>
+    <mergeCell ref="AG5:AG7"/>
+    <mergeCell ref="T5:AF5"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="Y6:Y7"/>
+    <mergeCell ref="Z6:Z7"/>
+    <mergeCell ref="AA6:AA7"/>
+    <mergeCell ref="AB6:AB7"/>
+    <mergeCell ref="AC6:AC7"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="U6:U7"/>
     <mergeCell ref="A1:AG1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A3:C3"/>
@@ -3559,22 +3928,23 @@
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="X3:AG3"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="W6:W7"/>
-    <mergeCell ref="X2:AE2"/>
-    <mergeCell ref="P4:AG4"/>
-    <mergeCell ref="K6:M7"/>
-    <mergeCell ref="AG5:AG7"/>
-    <mergeCell ref="T5:AF5"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="Y6:Y7"/>
-    <mergeCell ref="Z6:Z7"/>
-    <mergeCell ref="AA6:AA7"/>
-    <mergeCell ref="AB6:AB7"/>
-    <mergeCell ref="AC6:AC7"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="C5:M5"/>
+    <mergeCell ref="AD6:AD7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="AE6:AE7"/>
+    <mergeCell ref="E6:J6"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="AF6:AF7"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="V6:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -3583,47 +3953,52 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB10EE2-F4C9-4D62-AA1D-041CAE80A87C}">
-  <dimension ref="F29:P51"/>
+  <dimension ref="F28:P51"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
+    <row r="28" spans="6:8">
+      <c r="F28" t="s">
+        <v>188</v>
+      </c>
+    </row>
     <row r="29" spans="6:8">
-      <c r="F29" s="98" t="s">
+      <c r="F29" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="G29" s="98"/>
-      <c r="H29" s="98"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="99"/>
     </row>
     <row r="30" spans="6:8">
-      <c r="F30" s="98"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="98"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="99"/>
     </row>
     <row r="43" spans="12:16">
-      <c r="L43" s="98" t="s">
+      <c r="L43" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="M43" s="98"/>
-      <c r="N43" s="98"/>
-      <c r="O43" s="98"/>
-      <c r="P43" s="98"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
     </row>
     <row r="50" spans="12:16" ht="14.5" customHeight="1">
-      <c r="L50" s="99" t="s">
+      <c r="L50" s="100" t="s">
         <v>184</v>
       </c>
-      <c r="M50" s="99"/>
-      <c r="N50" s="99"/>
-      <c r="O50" s="98" t="s">
+      <c r="M50" s="100"/>
+      <c r="N50" s="100"/>
+      <c r="O50" s="99" t="s">
         <v>183</v>
       </c>
-      <c r="P50" s="98"/>
+      <c r="P50" s="99"/>
     </row>
     <row r="51" spans="12:16">
-      <c r="L51" s="99"/>
-      <c r="M51" s="99"/>
-      <c r="N51" s="99"/>
-      <c r="O51" s="98"/>
-      <c r="P51" s="98"/>
+      <c r="L51" s="100"/>
+      <c r="M51" s="100"/>
+      <c r="N51" s="100"/>
+      <c r="O51" s="99"/>
+      <c r="P51" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3638,6 +4013,365 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34448882-EE09-4FF8-BF45-79156CEBEDCF}">
+  <dimension ref="A9:G64"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" customWidth="1"/>
+    <col min="6" max="6" width="22.1796875" customWidth="1"/>
+    <col min="7" max="7" width="29.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="2:7">
+      <c r="B9" s="102" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="112" t="s">
+        <v>228</v>
+      </c>
+      <c r="G9" s="112" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="B18" s="102" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="102" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="F20" s="102" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E21" t="s">
+        <v>194</v>
+      </c>
+      <c r="F21" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C23" t="s">
+        <v>227</v>
+      </c>
+      <c r="E23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F23" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C24" t="s">
+        <v>220</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="B25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="104"/>
+      <c r="B27" s="104"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="B38" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="C38" s="106" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" s="111"/>
+      <c r="E38" s="109" t="s">
+        <v>201</v>
+      </c>
+      <c r="F38" s="105" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C39" s="107" t="s">
+        <v>230</v>
+      </c>
+      <c r="D39" s="111"/>
+      <c r="E39" s="110" t="s">
+        <v>207</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" s="108" t="s">
+        <v>215</v>
+      </c>
+      <c r="D40" s="111"/>
+      <c r="E40" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C41" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="D41" s="111"/>
+      <c r="E41" s="110" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" s="108" t="s">
+        <v>217</v>
+      </c>
+      <c r="D42" s="111"/>
+      <c r="E42" s="110" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="B43" s="1"/>
+      <c r="C43" s="107"/>
+      <c r="D43" s="111"/>
+      <c r="E43" s="110" t="s">
+        <v>208</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="1"/>
+      <c r="C44" s="107"/>
+      <c r="D44" s="111"/>
+      <c r="E44" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="103"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="103" t="s">
+        <v>192</v>
+      </c>
+      <c r="B55" s="103"/>
+      <c r="C55" s="103"/>
+      <c r="D55" s="103"/>
+      <c r="E55" s="103"/>
+      <c r="F55" s="103"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="B56" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" s="102"/>
+      <c r="E56" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="F56" s="102"/>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="B57" s="102" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="102" t="s">
+        <v>237</v>
+      </c>
+      <c r="D57" s="102"/>
+      <c r="E57" s="102" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="B58" t="s">
+        <v>210</v>
+      </c>
+      <c r="C58" t="s">
+        <v>239</v>
+      </c>
+      <c r="E58" t="s">
+        <v>239</v>
+      </c>
+      <c r="F58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="B59" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="B60" s="104"/>
+      <c r="C60" s="104"/>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="B61" t="s">
+        <v>211</v>
+      </c>
+      <c r="C61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" t="s">
+        <v>212</v>
+      </c>
+      <c r="F61" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="B63" t="s">
+        <v>233</v>
+      </c>
+      <c r="C63" t="s">
+        <v>235</v>
+      </c>
+      <c r="F63" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="F64" s="9" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A55:F55"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA80F6E5-4549-4ACD-B4F1-E6F5B68EB513}">
   <dimension ref="A1:K93"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -7012,7 +7746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D45D212-A622-4184-9BAC-B2149DEC6228}">
   <dimension ref="C1:F93"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -8330,7 +9064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A55A023-2F32-45C8-A00B-505296C005DC}">
   <dimension ref="A1:AB1086"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -73172,7 +73906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC37F13B-93AB-4CF8-AFCE-A0524EBA5C24}">
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -73184,12 +73918,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.5">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="12" t="s">

--- a/10aug2026/Surveyv + Gpx.xlsx
+++ b/10aug2026/Surveyv + Gpx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Barqaab\10aug2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E77642C0-4D62-410A-ACC9-C0806D88CD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787F8AD2-9B2F-4F0A-8031-2D34DEBF32DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HtSurveyForm - 081025" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3427" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3445" uniqueCount="264">
   <si>
     <t>Data Form for HT (GIS Survey Barqaab - PPL - OMS Consortium)</t>
   </si>
@@ -907,6 +907,60 @@
   <si>
     <t>ag_con</t>
   </si>
+  <si>
+    <t>2/0 AWG</t>
+  </si>
+  <si>
+    <t>4/0 AWG</t>
+  </si>
+  <si>
+    <t>500 MCM</t>
+  </si>
+  <si>
+    <t>ANT</t>
+  </si>
+  <si>
+    <t>DOG</t>
+  </si>
+  <si>
+    <t>GOPHER</t>
+  </si>
+  <si>
+    <t>OSPREY</t>
+  </si>
+  <si>
+    <t>PANTHER</t>
+  </si>
+  <si>
+    <t>RABBIT</t>
+  </si>
+  <si>
+    <t>WASP</t>
+  </si>
+  <si>
+    <t>220 MM</t>
+  </si>
+  <si>
+    <t>240 MM</t>
+  </si>
+  <si>
+    <t>120 MCM</t>
+  </si>
+  <si>
+    <t>350 MCM</t>
+  </si>
+  <si>
+    <t>240 MCM</t>
+  </si>
+  <si>
+    <t>Steel Wire</t>
+  </si>
+  <si>
+    <t>T Wire</t>
+  </si>
+  <si>
+    <t>Telephone Pole</t>
+  </si>
 </sst>
 </file>
 
@@ -1261,7 +1315,7 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1519,6 +1573,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Accent2" xfId="4" builtinId="33"/>
@@ -2030,7 +2086,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
+      <xdr:colOff>49389</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
@@ -2112,15 +2168,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>311150</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>143228</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>39158</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2143,8 +2199,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8591550" y="9436100"/>
-          <a:ext cx="1238250" cy="4867275"/>
+          <a:off x="8806039" y="9682339"/>
+          <a:ext cx="1232605" cy="4848930"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3953,8 +4009,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB10EE2-F4C9-4D62-AA1D-041CAE80A87C}">
-  <dimension ref="F28:P51"/>
+  <dimension ref="F28:S71"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="19" max="19" width="15.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="28" spans="6:8">
       <c r="F28" t="s">
@@ -3982,7 +4041,7 @@
       <c r="O43" s="99"/>
       <c r="P43" s="99"/>
     </row>
-    <row r="50" spans="12:16" ht="14.5" customHeight="1">
+    <row r="50" spans="12:19" ht="14.5" customHeight="1">
       <c r="L50" s="100" t="s">
         <v>184</v>
       </c>
@@ -3993,12 +4052,102 @@
       </c>
       <c r="P50" s="99"/>
     </row>
-    <row r="51" spans="12:16">
+    <row r="51" spans="12:19">
       <c r="L51" s="100"/>
       <c r="M51" s="100"/>
       <c r="N51" s="100"/>
       <c r="O51" s="99"/>
       <c r="P51" s="99"/>
+    </row>
+    <row r="54" spans="12:19">
+      <c r="S54" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="55" spans="12:19">
+      <c r="S55" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="12:19">
+      <c r="S56" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="57" spans="12:19">
+      <c r="S57" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="58" spans="12:19">
+      <c r="S58" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" spans="12:19">
+      <c r="S59" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="60" spans="12:19">
+      <c r="S60" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" spans="12:19">
+      <c r="S61" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="12:19">
+      <c r="S62" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="63" spans="12:19">
+      <c r="S63" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="64" spans="12:19">
+      <c r="S64" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="65" spans="19:19">
+      <c r="S65" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="66" spans="19:19">
+      <c r="S66" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="67" spans="19:19">
+      <c r="S67" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="68" spans="19:19">
+      <c r="S68" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="69" spans="19:19">
+      <c r="S69" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="70" spans="19:19">
+      <c r="S70" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="71" spans="19:19">
+      <c r="S71" t="s">
+        <v>263</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4128,7 +4277,7 @@
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="104"/>
+      <c r="A27" s="113"/>
       <c r="B27" s="104"/>
       <c r="C27" s="104"/>
       <c r="D27" s="104"/>
@@ -4136,10 +4285,10 @@
       <c r="F27" s="104"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="103" t="s">
+      <c r="A37" s="114"/>
+      <c r="B37" s="103" t="s">
         <v>192</v>
       </c>
-      <c r="B37" s="103"/>
       <c r="C37" s="103"/>
       <c r="D37" s="103"/>
       <c r="E37" s="103"/>
@@ -4362,9 +4511,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A55:F55"/>
+    <mergeCell ref="B37:F37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
